--- a/自然（しぜん）.xlsx
+++ b/自然（しぜん）.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\苗欣奕的东西\折跃\Japanese\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A1C863-B726-441B-8B78-53A60E482A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A06E99D-712E-4430-964A-477F4E420C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3476,7 +3476,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:G35"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="5" width="8.88671875" style="1"/>
@@ -3485,7 +3485,8 @@
     <col min="8" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="2" spans="1:7" ht="39.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>146</v>
       </c>
